--- a/src/assets/files/sample_upload_projects_with_milestones_tasks.xlsx
+++ b/src/assets/files/sample_upload_projects_with_milestones_tasks.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rehab.zafar\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rehab.zafar\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53A03A17-286C-40CF-8319-FA7D0AE695A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C14A83B-9E5B-410B-9F9A-766F87F4515B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="47">
   <si>
     <t>high</t>
   </si>
@@ -49,9 +49,6 @@
     <t>project_manager</t>
   </si>
   <si>
-    <t>project_department</t>
-  </si>
-  <si>
     <t>project_priority</t>
   </si>
   <si>
@@ -94,15 +91,6 @@
     <t>task_description</t>
   </si>
   <si>
-    <t>Information Technology</t>
-  </si>
-  <si>
-    <t>sana.asghar@srl.com.pk</t>
-  </si>
-  <si>
-    <t>rehab.zafar@srl.com.pk, sana.asghar@srl.com.pk,bilal.iqbal@srl.com.pk</t>
-  </si>
-  <si>
     <t>api development, reactjs, fastapi, python</t>
   </si>
   <si>
@@ -133,16 +121,46 @@
     <t>Bugs, Fixing, Api</t>
   </si>
   <si>
-    <t>Project 1</t>
-  </si>
-  <si>
-    <t>project 2</t>
-  </si>
-  <si>
     <t>Milestone 1</t>
   </si>
   <si>
-    <t>Task 1</t>
+    <t>project_workspace</t>
+  </si>
+  <si>
+    <t>sapphire portal</t>
+  </si>
+  <si>
+    <t>task_teams</t>
+  </si>
+  <si>
+    <t>cloud team, D365</t>
+  </si>
+  <si>
+    <t>rehab.zafar@srl.com.pk, rehab.zafar@srl.com.pk,bilal.iqbal@srl.com.pk</t>
+  </si>
+  <si>
+    <t>Task 4</t>
+  </si>
+  <si>
+    <t>task_status</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>Project Management System</t>
+  </si>
+  <si>
+    <t>Replenishment</t>
+  </si>
+  <si>
+    <t>marketing, cloud team</t>
+  </si>
+  <si>
+    <t>rehab.zafar@srl.com.pk, rehab.zafar@srl.com.pk,bilal.iqbal@srl.com.pk,kinza.amjad@srl.com.pk</t>
   </si>
 </sst>
 </file>
@@ -210,13 +228,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -556,34 +575,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U23"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="26.77734375" customWidth="1"/>
-    <col min="5" max="5" width="21.109375" customWidth="1"/>
-    <col min="6" max="6" width="34.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="60" customWidth="1"/>
-    <col min="8" max="8" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="31.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="42.21875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="81.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="31.21875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.77734375" customWidth="1"/>
+    <col min="19" max="19" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="42.77734375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>8</v>
@@ -601,54 +625,60 @@
         <v>7</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>1</v>
@@ -660,19 +690,19 @@
         <v>45971</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="H2" t="s">
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="K2" s="3">
         <v>45597</v>
@@ -684,39 +714,45 @@
         <v>0</v>
       </c>
       <c r="N2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="O2" t="s">
-        <v>40</v>
-      </c>
-      <c r="P2" s="3">
+        <v>39</v>
+      </c>
+      <c r="P2" s="4">
         <v>45597</v>
       </c>
-      <c r="Q2" s="3">
-        <v>45598</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="Q2" s="4">
+        <v>45622</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" t="s">
         <v>0</v>
       </c>
-      <c r="S2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="T2" t="s">
-        <v>31</v>
+      <c r="T2" s="2" t="s">
+        <v>1</v>
       </c>
       <c r="U2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+      <c r="V2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3">
         <v>45597</v>
@@ -725,19 +761,19 @@
         <v>45971</v>
       </c>
       <c r="F3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" t="s">
         <v>33</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J3" t="s">
-        <v>39</v>
       </c>
       <c r="K3" s="3">
         <v>45597</v>
@@ -749,31 +785,37 @@
         <v>2</v>
       </c>
       <c r="N3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="O3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P3" s="3">
+        <v>39</v>
+      </c>
+      <c r="P3" s="4">
         <v>45597</v>
       </c>
-      <c r="Q3" s="3">
-        <v>45598</v>
-      </c>
-      <c r="R3" t="s">
+      <c r="Q3" s="4">
+        <v>45624</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="S3" t="s">
         <v>0</v>
       </c>
-      <c r="S3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="T3" t="s">
-        <v>36</v>
+      <c r="T3" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="U3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V3" t="s">
+        <v>45</v>
+      </c>
+      <c r="W3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C4" s="2"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -782,9 +824,10 @@
       <c r="L4" s="3"/>
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
-      <c r="S4" s="2"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="R4" s="3"/>
+      <c r="T4" s="2"/>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C5" s="2"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -793,9 +836,10 @@
       <c r="L5" s="3"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
-      <c r="S5" s="2"/>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="R5" s="3"/>
+      <c r="T5" s="2"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C6" s="2"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -804,9 +848,10 @@
       <c r="L6" s="3"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
-      <c r="S6" s="2"/>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="R6" s="3"/>
+      <c r="T6" s="2"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C7" s="2"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -815,9 +860,10 @@
       <c r="L7" s="3"/>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
-      <c r="S7" s="2"/>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="R7" s="3"/>
+      <c r="T7" s="2"/>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C8" s="2"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -826,9 +872,10 @@
       <c r="L8" s="3"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
-      <c r="S8" s="2"/>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="R8" s="3"/>
+      <c r="T8" s="2"/>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C9" s="2"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -837,9 +884,10 @@
       <c r="L9" s="3"/>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
-      <c r="S9" s="2"/>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="R9" s="3"/>
+      <c r="T9" s="2"/>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C10" s="2"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -848,9 +896,10 @@
       <c r="L10" s="3"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
-      <c r="S10" s="2"/>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="R10" s="3"/>
+      <c r="T10" s="2"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C11" s="2"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -859,9 +908,10 @@
       <c r="L11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-      <c r="S11" s="2"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="R11" s="3"/>
+      <c r="T11" s="2"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C12" s="2"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -870,9 +920,10 @@
       <c r="L12" s="3"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
-      <c r="S12" s="2"/>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="R12" s="3"/>
+      <c r="T12" s="2"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C13" s="2"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -881,9 +932,10 @@
       <c r="L13" s="3"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
-      <c r="S13" s="2"/>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="R13" s="3"/>
+      <c r="T13" s="2"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C14" s="2"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -892,9 +944,10 @@
       <c r="L14" s="3"/>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
-      <c r="S14" s="2"/>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="R14" s="3"/>
+      <c r="T14" s="2"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C15" s="2"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -903,9 +956,10 @@
       <c r="L15" s="3"/>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
-      <c r="S15" s="2"/>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="R15" s="3"/>
+      <c r="T15" s="2"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="C16" s="2"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -914,9 +968,10 @@
       <c r="L16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-      <c r="S16" s="2"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="R16" s="3"/>
+      <c r="T16" s="2"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C17" s="2"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -925,9 +980,10 @@
       <c r="L17" s="3"/>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
-      <c r="S17" s="2"/>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="R17" s="3"/>
+      <c r="T17" s="2"/>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C18" s="2"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -936,9 +992,10 @@
       <c r="L18" s="3"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
-      <c r="S18" s="2"/>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="R18" s="3"/>
+      <c r="T18" s="2"/>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C19" s="2"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -947,9 +1004,10 @@
       <c r="L19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-      <c r="S19" s="2"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="R19" s="3"/>
+      <c r="T19" s="2"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C20" s="2"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -958,9 +1016,10 @@
       <c r="L20" s="3"/>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
-      <c r="S20" s="2"/>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="R20" s="3"/>
+      <c r="T20" s="2"/>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C21" s="2"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -969,9 +1028,10 @@
       <c r="L21" s="3"/>
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
-      <c r="S21" s="2"/>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="R21" s="3"/>
+      <c r="T21" s="2"/>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C22" s="2"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -980,9 +1040,10 @@
       <c r="L22" s="3"/>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
-      <c r="S22" s="2"/>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.3">
+      <c r="R22" s="3"/>
+      <c r="T22" s="2"/>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C23" s="2"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
@@ -991,16 +1052,17 @@
       <c r="L23" s="3"/>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
-      <c r="S23" s="2"/>
+      <c r="R23" s="3"/>
+      <c r="T23" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{0C4AF39A-1EB4-46FA-BBC8-FB013FBD5606}"/>
     <hyperlink ref="G2" r:id="rId2" display="rehab.zafar@srl.com.pk" xr:uid="{C60875F6-8B89-4660-95C3-D9862CBF4F98}"/>
-    <hyperlink ref="S2" r:id="rId3" xr:uid="{B2982C5F-F53E-4DB8-9851-605E06CD3C21}"/>
+    <hyperlink ref="T2" r:id="rId3" xr:uid="{B2982C5F-F53E-4DB8-9851-605E06CD3C21}"/>
     <hyperlink ref="C3" r:id="rId4" xr:uid="{F6BA6D6F-602E-4742-B7B5-0AFF0F6DF311}"/>
     <hyperlink ref="G3" r:id="rId5" display="rehab.zafar@srl.com.pk" xr:uid="{42B8D549-A27E-45FB-88FE-EC603E5DA0BB}"/>
-    <hyperlink ref="S3" r:id="rId6" xr:uid="{EE8B2673-6073-4CA6-88F8-74FA5A7AADF3}"/>
+    <hyperlink ref="T3" r:id="rId6" xr:uid="{EE8B2673-6073-4CA6-88F8-74FA5A7AADF3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
